--- a/menu.xlsx
+++ b/menu.xlsx
@@ -427,7 +427,7 @@
         <v>Food</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0.12</v>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -427,7 +427,7 @@
         <v>Food</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0.12</v>
